--- a/AAII_Financials/Yearly/QSR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/QSR_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
   <si>
     <t>QSR</t>
   </si>
@@ -656,159 +656,171 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7022000</v>
+      </c>
+      <c r="E8" s="3">
         <v>6505000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5739000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4968000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5603000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5357000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4576100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4145800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4052200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1198800</v>
       </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2428000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2312000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1890000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1610000</v>
-      </c>
-      <c r="G9" s="3">
-        <v>1818000</v>
       </c>
       <c r="H9" s="3">
         <v>1818000</v>
       </c>
       <c r="I9" s="3">
+        <v>1818000</v>
+      </c>
+      <c r="J9" s="3">
         <v>1850300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1727300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1809500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>156400</v>
       </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4594000</v>
+      </c>
+      <c r="E10" s="3">
         <v>4193000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3849000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3358000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3785000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3539000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2725800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2418500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2242700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1042400</v>
       </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -822,8 +834,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -854,9 +867,12 @@
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -887,75 +903,84 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>55000</v>
+      </c>
+      <c r="E14" s="3">
         <v>57000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>108000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>121000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>62000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>66000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>164300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>18000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>158000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>284400</v>
       </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="3">
         <v>25000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>20000</v>
-      </c>
-      <c r="F15" s="3">
-        <v>19000</v>
       </c>
       <c r="G15" s="3">
         <v>19000</v>
       </c>
       <c r="H15" s="3">
+        <v>19000</v>
+      </c>
+      <c r="I15" s="3">
         <v>20000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>22900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>21700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>17000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>14000</v>
       </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -966,74 +991,81 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4987000</v>
+      </c>
+      <c r="E17" s="3">
         <v>4607000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3871000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3644000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3619000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3440000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2962200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2479100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2900000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1173100</v>
       </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2035000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1898000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1868000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1324000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1984000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1917000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1613900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1666700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1152200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>25700</v>
       </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1047,173 +1079,189 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>184000</v>
+      </c>
+      <c r="E20" s="3">
         <v>9000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-77000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-24000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>64000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>15000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>26400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>4100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2800</v>
       </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2410000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2097000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1992000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1489000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2233000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2112000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1822300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1842900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1335800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>97300</v>
       </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>766000</v>
+      </c>
+      <c r="E22" s="3">
         <v>542000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>428000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>484000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>596000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>550000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>538600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>471000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>479900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>282500</v>
       </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1453000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1365000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1363000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>816000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1452000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1382000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1101700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1199800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>673900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-254000</v>
       </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-265000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-117000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>110000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>66000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>341000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>229000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>64300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>243900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>162200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>15300</v>
       </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1244,75 +1292,84 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1718000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1482000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1253000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>750000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1111000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1153000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1037400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>955900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>511700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-269300</v>
       </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1190000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1008000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>838000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>486000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>643000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>621000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>428200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>345600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>103900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-398800</v>
       </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1343,9 +1400,12 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1361,14 +1421,14 @@
       <c r="G29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H29" s="3">
+      <c r="H29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I29" s="3">
         <v>-9000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>197900</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1376,9 +1436,12 @@
       <c r="L29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1409,9 +1472,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1442,75 +1508,84 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-184000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-9000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>77000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>24000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-64000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-15000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-26400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-4100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2800</v>
       </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1190000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1008000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>838000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>486000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>643000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>612000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>626100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>345600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>103900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-398800</v>
       </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1541,80 +1616,89 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1190000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1008000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>838000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>486000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>643000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>612000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>626100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>345600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>103900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-398800</v>
       </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1628,8 +1712,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1643,41 +1728,45 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1139000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1178000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1087000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1560000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1533000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>913000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1097400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1460400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>757800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1803200</v>
       </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1708,240 +1797,264 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>749000</v>
+      </c>
+      <c r="E43" s="3">
         <v>614000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>547000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>536000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>527000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>452000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>488800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>403500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>443500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>459500</v>
       </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>166000</v>
+      </c>
+      <c r="E44" s="3">
         <v>133000</v>
-      </c>
-      <c r="E44" s="3">
-        <v>96000</v>
       </c>
       <c r="F44" s="3">
         <v>96000</v>
       </c>
       <c r="G44" s="3">
+        <v>96000</v>
+      </c>
+      <c r="H44" s="3">
         <v>84000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>75000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>78000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>71800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>81300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>97800</v>
       </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>119000</v>
+      </c>
+      <c r="E45" s="3">
         <v>123000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>86000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>72000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>52000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>60000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>168700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>161300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>86900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>300800</v>
       </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2173000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2048000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1816000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2264000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2196000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1500000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1749600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2097000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1369500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2640800</v>
       </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3">
         <v>82000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>80000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>66000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>48000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>54000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>71300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>91900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>117200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>140500</v>
       </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3074000</v>
+      </c>
+      <c r="E48" s="3">
         <v>3032000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3165000</v>
-      </c>
-      <c r="F48" s="3">
-        <v>3183000</v>
       </c>
       <c r="G48" s="3">
         <v>3183000</v>
       </c>
       <c r="H48" s="3">
+        <v>3183000</v>
+      </c>
+      <c r="I48" s="3">
         <v>1996000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4889900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2054700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2150600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5098700</v>
       </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>16882000</v>
+      </c>
+      <c r="E49" s="3">
         <v>16679000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>17423000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>16440000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>16214000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>15949000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>16844500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>13903100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>13722200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>15680800</v>
       </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1972,9 +2085,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2005,42 +2121,48 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1262000</v>
+      </c>
+      <c r="E52" s="3">
         <v>905000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>762000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>824000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>719000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>642000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>424800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>978200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1051600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>582900</v>
       </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2071,42 +2193,48 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>23391000</v>
+      </c>
+      <c r="E54" s="3">
         <v>22746000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>23246000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>22777000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>22360000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>20141000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>21223500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>19124900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>18411100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>21343000</v>
       </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2120,8 +2248,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2135,206 +2264,225 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>790000</v>
+      </c>
+      <c r="E57" s="3">
         <v>758000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>614000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>464000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>644000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>513000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>496200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>369800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>361500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>223000</v>
       </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>101000</v>
+      </c>
+      <c r="E58" s="3">
         <v>127000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>96000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>111000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>101000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>91000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>78200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>93900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>56100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2173600</v>
       </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1253000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1231000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1168000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1026000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>958000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>804000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1191400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>747000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>703400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>594000</v>
       </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2144000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2116000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1878000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1601000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1703000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1408000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1655000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1210700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1121000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1945800</v>
       </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>13166000</v>
+      </c>
+      <c r="E61" s="3">
         <v>13150000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>13249000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>12712000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12047000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>12049000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>12044700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8628600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8665700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9070200</v>
       </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3351000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3212000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4266000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4743000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4351000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3066000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2963200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2500000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2414700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2690600</v>
       </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2365,9 +2513,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2398,9 +2549,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2431,42 +2585,48 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>20525000</v>
+      </c>
+      <c r="E66" s="3">
         <v>20247000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>21009000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>20610000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>19870000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>18530000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>18997100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>14125400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13777500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>16167800</v>
       </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2480,8 +2640,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2512,9 +2673,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2545,9 +2709,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2570,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="J70" s="3">
-        <v>3297000</v>
+        <v>0</v>
       </c>
       <c r="K70" s="3">
         <v>3297000</v>
@@ -2578,9 +2745,12 @@
       <c r="L70" s="3">
         <v>3297000</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>3297000</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2611,42 +2781,48 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1599000</v>
+      </c>
+      <c r="E72" s="3">
         <v>1121000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>791000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>622000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>775000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>674000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>650600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>445700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>245800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>231000</v>
       </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2677,9 +2853,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2710,9 +2889,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2743,42 +2925,48 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2866000</v>
+      </c>
+      <c r="E76" s="3">
         <v>2499000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2237000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2167000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2490000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1611000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2226400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1702500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1336600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1878200</v>
       </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2809,80 +2997,89 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1190000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1008000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>838000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>486000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>643000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>612000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>626100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>345600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>103900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-398800</v>
       </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2896,41 +3093,45 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>191000</v>
+      </c>
+      <c r="E83" s="3">
         <v>190000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>201000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>189000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>185000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>180000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>182000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>172100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>182000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>68800</v>
       </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2961,9 +3162,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2994,9 +3198,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3027,9 +3234,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3060,9 +3270,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3093,42 +3306,48 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1323000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1490000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1726000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>921000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1476000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1165000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1391000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1269000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1204800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>259300</v>
       </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3142,41 +3361,45 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-120000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-106000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-117000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-62000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-86000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-37000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-33700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-115300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-38700</v>
       </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3207,9 +3430,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3240,42 +3466,48 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-64000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1103000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-79000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-30000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-44000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-858000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>26900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-61500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-7790800</v>
       </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3289,41 +3521,45 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-990000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-971000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-974000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-959000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-901000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-728000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-664000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-538100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-362400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-105600</v>
       </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3354,9 +3590,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3387,9 +3626,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3420,106 +3662,118 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1374000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1307000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1093000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-821000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-842000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1285000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-936000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-590900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2115200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>8565600</v>
       </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-28000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-3000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>6000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>16000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-20000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>24000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-73500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-17800</v>
       </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="E102" s="3">
         <v>91000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-473000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>27000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>620000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-184000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-379000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>702600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1045400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1016300</v>
       </c>
-      <c r="M102" s="3"/>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/QSR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/QSR_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="92">
   <si>
     <t>QSR</t>
   </si>
@@ -735,7 +735,7 @@
         <v>5357000</v>
       </c>
       <c r="J8" s="3">
-        <v>4576100</v>
+        <v>4576000</v>
       </c>
       <c r="K8" s="3">
         <v>4145800</v>
@@ -753,25 +753,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2428000</v>
+        <v>4220000</v>
       </c>
       <c r="E9" s="3">
-        <v>2312000</v>
+        <v>3907000</v>
       </c>
       <c r="F9" s="3">
-        <v>1890000</v>
+        <v>3365000</v>
       </c>
       <c r="G9" s="3">
-        <v>1610000</v>
+        <v>2995000</v>
       </c>
       <c r="H9" s="3">
-        <v>1818000</v>
+        <v>3211000</v>
       </c>
       <c r="I9" s="3">
-        <v>1818000</v>
+        <v>2240000</v>
       </c>
       <c r="J9" s="3">
-        <v>1850300</v>
+        <v>2328000</v>
       </c>
       <c r="K9" s="3">
         <v>1727300</v>
@@ -789,25 +789,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>4594000</v>
+        <v>2802000</v>
       </c>
       <c r="E10" s="3">
-        <v>4193000</v>
+        <v>2598000</v>
       </c>
       <c r="F10" s="3">
-        <v>3849000</v>
+        <v>2374000</v>
       </c>
       <c r="G10" s="3">
-        <v>3358000</v>
+        <v>1973000</v>
       </c>
       <c r="H10" s="3">
-        <v>3785000</v>
+        <v>2392000</v>
       </c>
       <c r="I10" s="3">
-        <v>3539000</v>
+        <v>3117000</v>
       </c>
       <c r="J10" s="3">
-        <v>2725800</v>
+        <v>2248000</v>
       </c>
       <c r="K10" s="3">
         <v>2418500</v>
@@ -913,25 +913,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>55000</v>
+        <v>90000</v>
       </c>
       <c r="E14" s="3">
-        <v>57000</v>
+        <v>85000</v>
       </c>
       <c r="F14" s="3">
-        <v>108000</v>
+        <v>128000</v>
       </c>
       <c r="G14" s="3">
-        <v>121000</v>
+        <v>127000</v>
       </c>
       <c r="H14" s="3">
-        <v>62000</v>
+        <v>69000</v>
       </c>
       <c r="I14" s="3">
-        <v>66000</v>
+        <v>85000</v>
       </c>
       <c r="J14" s="3">
-        <v>164300</v>
+        <v>217000</v>
       </c>
       <c r="K14" s="3">
         <v>18000</v>
@@ -948,26 +948,26 @@
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>8</v>
+      <c r="D15" s="3">
+        <v>191000</v>
       </c>
       <c r="E15" s="3">
-        <v>25000</v>
+        <v>190000</v>
       </c>
       <c r="F15" s="3">
-        <v>20000</v>
+        <v>201000</v>
       </c>
       <c r="G15" s="3">
-        <v>19000</v>
+        <v>189000</v>
       </c>
       <c r="H15" s="3">
-        <v>19000</v>
+        <v>185000</v>
       </c>
       <c r="I15" s="3">
-        <v>20000</v>
+        <v>180000</v>
       </c>
       <c r="J15" s="3">
-        <v>22900</v>
+        <v>182000</v>
       </c>
       <c r="K15" s="3">
         <v>21700</v>
@@ -998,25 +998,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4987000</v>
+        <v>4885000</v>
       </c>
       <c r="E17" s="3">
-        <v>4607000</v>
+        <v>4482000</v>
       </c>
       <c r="F17" s="3">
-        <v>3871000</v>
+        <v>3815000</v>
       </c>
       <c r="G17" s="3">
-        <v>3644000</v>
+        <v>3378000</v>
       </c>
       <c r="H17" s="3">
-        <v>3619000</v>
+        <v>3576000</v>
       </c>
       <c r="I17" s="3">
-        <v>3440000</v>
+        <v>3410000</v>
       </c>
       <c r="J17" s="3">
-        <v>2962200</v>
+        <v>2681000</v>
       </c>
       <c r="K17" s="3">
         <v>2479100</v>
@@ -1034,25 +1034,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2035000</v>
+        <v>2137000</v>
       </c>
       <c r="E18" s="3">
-        <v>1898000</v>
+        <v>2023000</v>
       </c>
       <c r="F18" s="3">
-        <v>1868000</v>
+        <v>1924000</v>
       </c>
       <c r="G18" s="3">
-        <v>1324000</v>
+        <v>1590000</v>
       </c>
       <c r="H18" s="3">
-        <v>1984000</v>
+        <v>2027000</v>
       </c>
       <c r="I18" s="3">
-        <v>1917000</v>
+        <v>1947000</v>
       </c>
       <c r="J18" s="3">
-        <v>1613900</v>
+        <v>1895000</v>
       </c>
       <c r="K18" s="3">
         <v>1666700</v>
@@ -1086,25 +1086,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>184000</v>
+        <v>12000</v>
       </c>
       <c r="E20" s="3">
-        <v>9000</v>
+        <v>40000</v>
       </c>
       <c r="F20" s="3">
-        <v>-77000</v>
+        <v>-72000</v>
       </c>
       <c r="G20" s="3">
-        <v>-24000</v>
+        <v>139000</v>
       </c>
       <c r="H20" s="3">
-        <v>64000</v>
+        <v>-26000</v>
       </c>
       <c r="I20" s="3">
-        <v>15000</v>
+        <v>-55000</v>
       </c>
       <c r="J20" s="3">
-        <v>26400</v>
+        <v>65000</v>
       </c>
       <c r="K20" s="3">
         <v>4100</v>
@@ -1122,25 +1122,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2410000</v>
+        <v>2316000</v>
       </c>
       <c r="E21" s="3">
-        <v>2097000</v>
+        <v>2173000</v>
       </c>
       <c r="F21" s="3">
-        <v>1992000</v>
+        <v>2197000</v>
       </c>
       <c r="G21" s="3">
-        <v>1489000</v>
+        <v>1640000</v>
       </c>
       <c r="H21" s="3">
-        <v>2233000</v>
+        <v>2238000</v>
       </c>
       <c r="I21" s="3">
-        <v>2112000</v>
+        <v>2182000</v>
       </c>
       <c r="J21" s="3">
-        <v>1822300</v>
+        <v>2012000</v>
       </c>
       <c r="K21" s="3">
         <v>1842900</v>
@@ -1158,25 +1158,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>766000</v>
+        <v>595000</v>
       </c>
       <c r="E22" s="3">
-        <v>542000</v>
+        <v>512000</v>
       </c>
       <c r="F22" s="3">
-        <v>428000</v>
+        <v>481000</v>
       </c>
       <c r="G22" s="3">
-        <v>484000</v>
+        <v>491000</v>
       </c>
       <c r="H22" s="3">
-        <v>596000</v>
+        <v>523000</v>
       </c>
       <c r="I22" s="3">
-        <v>550000</v>
+        <v>521000</v>
       </c>
       <c r="J22" s="3">
-        <v>538600</v>
+        <v>505000</v>
       </c>
       <c r="K22" s="3">
         <v>471000</v>
@@ -1212,7 +1212,7 @@
         <v>1382000</v>
       </c>
       <c r="J23" s="3">
-        <v>1101700</v>
+        <v>1101000</v>
       </c>
       <c r="K23" s="3">
         <v>1199800</v>
@@ -1245,10 +1245,10 @@
         <v>341000</v>
       </c>
       <c r="I24" s="3">
-        <v>229000</v>
+        <v>238000</v>
       </c>
       <c r="J24" s="3">
-        <v>64300</v>
+        <v>-134000</v>
       </c>
       <c r="K24" s="3">
         <v>243900</v>
@@ -1317,10 +1317,10 @@
         <v>1111000</v>
       </c>
       <c r="I26" s="3">
-        <v>1153000</v>
+        <v>1144000</v>
       </c>
       <c r="J26" s="3">
-        <v>1037400</v>
+        <v>1235000</v>
       </c>
       <c r="K26" s="3">
         <v>955900</v>
@@ -1353,10 +1353,10 @@
         <v>643000</v>
       </c>
       <c r="I27" s="3">
-        <v>621000</v>
+        <v>612000</v>
       </c>
       <c r="J27" s="3">
-        <v>428200</v>
+        <v>626000</v>
       </c>
       <c r="K27" s="3">
         <v>345600</v>
@@ -1409,26 +1409,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>-9000</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>197900</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1518,25 +1518,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-184000</v>
+        <v>-12000</v>
       </c>
       <c r="E32" s="3">
-        <v>-9000</v>
+        <v>-40000</v>
       </c>
       <c r="F32" s="3">
-        <v>77000</v>
+        <v>72000</v>
       </c>
       <c r="G32" s="3">
-        <v>24000</v>
+        <v>-139000</v>
       </c>
       <c r="H32" s="3">
-        <v>-64000</v>
+        <v>26000</v>
       </c>
       <c r="I32" s="3">
-        <v>-15000</v>
+        <v>55000</v>
       </c>
       <c r="J32" s="3">
-        <v>-26400</v>
+        <v>-65000</v>
       </c>
       <c r="K32" s="3">
         <v>-4100</v>
@@ -1572,7 +1572,7 @@
         <v>612000</v>
       </c>
       <c r="J33" s="3">
-        <v>626100</v>
+        <v>648000</v>
       </c>
       <c r="K33" s="3">
         <v>345600</v>
@@ -1644,7 +1644,7 @@
         <v>612000</v>
       </c>
       <c r="J35" s="3">
-        <v>626100</v>
+        <v>648000</v>
       </c>
       <c r="K35" s="3">
         <v>345600</v>
@@ -1753,7 +1753,7 @@
         <v>913000</v>
       </c>
       <c r="J41" s="3">
-        <v>1097400</v>
+        <v>1097000</v>
       </c>
       <c r="K41" s="3">
         <v>1460400</v>
@@ -1825,7 +1825,7 @@
         <v>452000</v>
       </c>
       <c r="J43" s="3">
-        <v>488800</v>
+        <v>489000</v>
       </c>
       <c r="K43" s="3">
         <v>403500</v>
@@ -1878,26 +1878,26 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>119000</v>
+      <c r="D45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E45" s="3">
-        <v>123000</v>
+        <v>7000</v>
       </c>
       <c r="F45" s="3">
-        <v>86000</v>
-      </c>
-      <c r="G45" s="3">
-        <v>72000</v>
-      </c>
-      <c r="H45" s="3">
-        <v>52000</v>
+        <v>2000</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I45" s="3">
-        <v>60000</v>
+        <v>7000</v>
       </c>
       <c r="J45" s="3">
-        <v>168700</v>
+        <v>1000</v>
       </c>
       <c r="K45" s="3">
         <v>161300</v>
@@ -1933,7 +1933,7 @@
         <v>1500000</v>
       </c>
       <c r="J46" s="3">
-        <v>1749600</v>
+        <v>1750000</v>
       </c>
       <c r="K46" s="3">
         <v>2097000</v>
@@ -1950,26 +1950,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>8</v>
+      <c r="D47" s="3">
+        <v>353000</v>
       </c>
       <c r="E47" s="3">
-        <v>82000</v>
+        <v>447000</v>
       </c>
       <c r="F47" s="3">
-        <v>80000</v>
+        <v>194000</v>
       </c>
       <c r="G47" s="3">
-        <v>66000</v>
+        <v>205000</v>
       </c>
       <c r="H47" s="3">
-        <v>48000</v>
+        <v>273000</v>
       </c>
       <c r="I47" s="3">
-        <v>54000</v>
+        <v>259000</v>
       </c>
       <c r="J47" s="3">
-        <v>71300</v>
+        <v>155000</v>
       </c>
       <c r="K47" s="3">
         <v>91900</v>
@@ -2005,7 +2005,7 @@
         <v>1996000</v>
       </c>
       <c r="J48" s="3">
-        <v>4889900</v>
+        <v>2133000</v>
       </c>
       <c r="K48" s="3">
         <v>2054700</v>
@@ -2041,7 +2041,7 @@
         <v>15949000</v>
       </c>
       <c r="J49" s="3">
-        <v>16844500</v>
+        <v>16844000</v>
       </c>
       <c r="K49" s="3">
         <v>13903100</v>
@@ -2131,25 +2131,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1262000</v>
+        <v>909000</v>
       </c>
       <c r="E52" s="3">
-        <v>905000</v>
+        <v>540000</v>
       </c>
       <c r="F52" s="3">
-        <v>762000</v>
+        <v>568000</v>
       </c>
       <c r="G52" s="3">
-        <v>824000</v>
+        <v>619000</v>
       </c>
       <c r="H52" s="3">
-        <v>719000</v>
+        <v>446000</v>
       </c>
       <c r="I52" s="3">
-        <v>642000</v>
+        <v>383000</v>
       </c>
       <c r="J52" s="3">
-        <v>424800</v>
+        <v>271000</v>
       </c>
       <c r="K52" s="3">
         <v>978200</v>
@@ -2221,7 +2221,7 @@
         <v>20141000</v>
       </c>
       <c r="J54" s="3">
-        <v>21223500</v>
+        <v>21224000</v>
       </c>
       <c r="K54" s="3">
         <v>19124900</v>
@@ -2289,7 +2289,7 @@
         <v>513000</v>
       </c>
       <c r="J57" s="3">
-        <v>496200</v>
+        <v>496000</v>
       </c>
       <c r="K57" s="3">
         <v>369800</v>
@@ -2307,25 +2307,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>101000</v>
+        <v>248000</v>
       </c>
       <c r="E58" s="3">
-        <v>127000</v>
+        <v>264000</v>
       </c>
       <c r="F58" s="3">
-        <v>96000</v>
+        <v>236000</v>
       </c>
       <c r="G58" s="3">
-        <v>111000</v>
+        <v>248000</v>
       </c>
       <c r="H58" s="3">
-        <v>101000</v>
+        <v>227000</v>
       </c>
       <c r="I58" s="3">
         <v>91000</v>
       </c>
       <c r="J58" s="3">
-        <v>78200</v>
+        <v>78000</v>
       </c>
       <c r="K58" s="3">
         <v>93900</v>
@@ -2343,25 +2343,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1253000</v>
+        <v>717000</v>
       </c>
       <c r="E59" s="3">
-        <v>1231000</v>
+        <v>735000</v>
       </c>
       <c r="F59" s="3">
-        <v>1168000</v>
+        <v>706000</v>
       </c>
       <c r="G59" s="3">
-        <v>1026000</v>
+        <v>611000</v>
       </c>
       <c r="H59" s="3">
-        <v>958000</v>
+        <v>571000</v>
       </c>
       <c r="I59" s="3">
-        <v>804000</v>
+        <v>525000</v>
       </c>
       <c r="J59" s="3">
-        <v>1191400</v>
+        <v>779000</v>
       </c>
       <c r="K59" s="3">
         <v>747000</v>
@@ -2415,25 +2415,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>13166000</v>
+        <v>14225000</v>
       </c>
       <c r="E61" s="3">
-        <v>13150000</v>
+        <v>14177000</v>
       </c>
       <c r="F61" s="3">
-        <v>13249000</v>
+        <v>14539000</v>
       </c>
       <c r="G61" s="3">
-        <v>12712000</v>
+        <v>14224000</v>
       </c>
       <c r="H61" s="3">
-        <v>12047000</v>
+        <v>13311000</v>
       </c>
       <c r="I61" s="3">
-        <v>12049000</v>
+        <v>12121000</v>
       </c>
       <c r="J61" s="3">
-        <v>12044700</v>
+        <v>12087000</v>
       </c>
       <c r="K61" s="3">
         <v>8628600</v>
@@ -2451,25 +2451,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3351000</v>
+        <v>350000</v>
       </c>
       <c r="E62" s="3">
-        <v>3212000</v>
+        <v>248000</v>
       </c>
       <c r="F62" s="3">
-        <v>4266000</v>
+        <v>987000</v>
       </c>
       <c r="G62" s="3">
-        <v>4743000</v>
+        <v>1180000</v>
       </c>
       <c r="H62" s="3">
-        <v>4351000</v>
+        <v>892000</v>
       </c>
       <c r="I62" s="3">
-        <v>3066000</v>
+        <v>903000</v>
       </c>
       <c r="J62" s="3">
-        <v>2963200</v>
+        <v>1304000</v>
       </c>
       <c r="K62" s="3">
         <v>2500000</v>
@@ -2595,25 +2595,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>20525000</v>
+        <v>18661000</v>
       </c>
       <c r="E66" s="3">
-        <v>20247000</v>
+        <v>18478000</v>
       </c>
       <c r="F66" s="3">
-        <v>21009000</v>
+        <v>19393000</v>
       </c>
       <c r="G66" s="3">
-        <v>20610000</v>
+        <v>19056000</v>
       </c>
       <c r="H66" s="3">
-        <v>19870000</v>
+        <v>18101000</v>
       </c>
       <c r="I66" s="3">
-        <v>18530000</v>
+        <v>16523000</v>
       </c>
       <c r="J66" s="3">
-        <v>18997100</v>
+        <v>16663000</v>
       </c>
       <c r="K66" s="3">
         <v>14125400</v>
@@ -2809,7 +2809,7 @@
         <v>674000</v>
       </c>
       <c r="J72" s="3">
-        <v>650600</v>
+        <v>651000</v>
       </c>
       <c r="K72" s="3">
         <v>445700</v>
@@ -2953,7 +2953,7 @@
         <v>1611000</v>
       </c>
       <c r="J76" s="3">
-        <v>2226400</v>
+        <v>2227000</v>
       </c>
       <c r="K76" s="3">
         <v>1702500</v>
@@ -3066,7 +3066,7 @@
         <v>612000</v>
       </c>
       <c r="J81" s="3">
-        <v>626100</v>
+        <v>648000</v>
       </c>
       <c r="K81" s="3">
         <v>345600</v>
@@ -3100,25 +3100,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>191000</v>
+        <v>154000</v>
       </c>
       <c r="E83" s="3">
-        <v>190000</v>
+        <v>151000</v>
       </c>
       <c r="F83" s="3">
-        <v>201000</v>
+        <v>160000</v>
       </c>
       <c r="G83" s="3">
-        <v>189000</v>
+        <v>146000</v>
       </c>
       <c r="H83" s="3">
-        <v>185000</v>
+        <v>141000</v>
       </c>
       <c r="I83" s="3">
-        <v>180000</v>
+        <v>110000</v>
       </c>
       <c r="J83" s="3">
-        <v>182000</v>
+        <v>110000</v>
       </c>
       <c r="K83" s="3">
         <v>172100</v>
@@ -3528,25 +3528,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-990000</v>
+        <v>990000</v>
       </c>
       <c r="E96" s="3">
-        <v>-971000</v>
+        <v>971000</v>
       </c>
       <c r="F96" s="3">
-        <v>-974000</v>
+        <v>974000</v>
       </c>
       <c r="G96" s="3">
-        <v>-959000</v>
+        <v>959000</v>
       </c>
       <c r="H96" s="3">
-        <v>-901000</v>
+        <v>901000</v>
       </c>
       <c r="I96" s="3">
-        <v>-728000</v>
+        <v>728000</v>
       </c>
       <c r="J96" s="3">
-        <v>-664000</v>
+        <v>0</v>
       </c>
       <c r="K96" s="3">
         <v>-538100</v>

--- a/AAII_Financials/Yearly/QSR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/QSR_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
   <si>
     <t>QSR</t>
   </si>
@@ -656,171 +656,183 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8406000</v>
+      </c>
+      <c r="E8" s="3">
         <v>7022000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6505000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5739000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4968000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5603000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5357000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4576000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4145800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4052200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1198800</v>
       </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>5382000</v>
+      </c>
+      <c r="E9" s="3">
         <v>4220000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3907000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3365000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2995000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3211000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2240000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2328000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1727300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1809500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>156400</v>
       </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3024000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2802000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2598000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2374000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1973000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2392000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3117000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2248000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2418500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2242700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1042400</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -835,8 +847,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -870,9 +883,12 @@
       <c r="M12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -906,81 +922,90 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>78000</v>
+      </c>
+      <c r="E14" s="3">
         <v>90000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>85000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>128000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>127000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>69000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>85000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>217000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>18000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>158000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>284400</v>
       </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>264000</v>
+      </c>
+      <c r="E15" s="3">
         <v>191000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>190000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>201000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>189000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>185000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>180000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>182000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>21700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>17000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>14000</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -992,80 +1017,87 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6082000</v>
+      </c>
+      <c r="E17" s="3">
         <v>4885000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4482000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3815000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3378000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3576000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3410000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2681000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2479100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2900000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1173100</v>
       </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2324000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2137000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2023000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1924000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1590000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2027000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1947000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1895000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1666700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1152200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>25700</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1080,188 +1112,204 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-140000</v>
+      </c>
+      <c r="E20" s="3">
         <v>12000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>40000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-72000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>139000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-26000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-55000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>65000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2800</v>
       </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2728000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2316000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2173000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2197000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1640000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2238000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2182000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2012000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1842900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1335800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>97300</v>
       </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>591000</v>
+      </c>
+      <c r="E22" s="3">
         <v>595000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>512000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>481000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>491000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>523000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>521000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>505000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>471000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>479900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>282500</v>
       </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1809000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1453000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1365000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1363000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>816000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1452000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1382000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1101000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1199800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>673900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-254000</v>
       </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>364000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-265000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-117000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>110000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>66000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>341000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>238000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-134000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>243900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>162200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>15300</v>
       </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1295,81 +1343,90 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1445000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1718000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1482000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1253000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>750000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1111000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1144000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1235000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>955900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>511700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-269300</v>
       </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1021000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1190000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1008000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>838000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>486000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>643000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>612000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>626000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>345600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>103900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-398800</v>
       </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1403,9 +1460,12 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1430,8 +1490,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>8</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>8</v>
@@ -1439,9 +1499,12 @@
       <c r="M29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1475,9 +1538,12 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1511,81 +1577,90 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>140000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-12000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-40000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>72000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-139000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>26000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>55000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-65000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2800</v>
       </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1021000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1190000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1008000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>838000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>486000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>643000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>612000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>648000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>345600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>103900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-398800</v>
       </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1619,86 +1694,95 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1021000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1190000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1008000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>838000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>486000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>643000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>612000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>648000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>345600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>103900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-398800</v>
       </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1713,8 +1797,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1729,49 +1814,53 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1334000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1139000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1178000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1087000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1560000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1533000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>913000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1097000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1460400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>757800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1803200</v>
       </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -1800,261 +1889,285 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>698000</v>
+      </c>
+      <c r="E43" s="3">
         <v>749000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>614000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>547000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>536000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>527000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>452000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>489000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>403500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>443500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>459500</v>
       </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>142000</v>
+      </c>
+      <c r="E44" s="3">
         <v>166000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>133000</v>
-      </c>
-      <c r="F44" s="3">
-        <v>96000</v>
       </c>
       <c r="G44" s="3">
         <v>96000</v>
       </c>
       <c r="H44" s="3">
+        <v>96000</v>
+      </c>
+      <c r="I44" s="3">
         <v>84000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>75000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>78000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>71800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>81300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>97800</v>
       </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D45" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2000</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3">
         <v>7000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>161300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>86900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>300800</v>
       </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2282000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2173000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2048000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1816000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2264000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2196000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1500000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1750000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2097000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1369500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2640800</v>
       </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>307000</v>
+      </c>
+      <c r="E47" s="3">
         <v>353000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>447000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>194000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>205000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>273000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>259000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>155000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>91900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>117200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>140500</v>
       </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4088000</v>
+      </c>
+      <c r="E48" s="3">
         <v>3074000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3032000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3165000</v>
-      </c>
-      <c r="G48" s="3">
-        <v>3183000</v>
       </c>
       <c r="H48" s="3">
         <v>3183000</v>
       </c>
       <c r="I48" s="3">
+        <v>3183000</v>
+      </c>
+      <c r="J48" s="3">
         <v>1996000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2133000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2054700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2150600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5098700</v>
       </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>16908000</v>
+      </c>
+      <c r="E49" s="3">
         <v>16882000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>16679000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>17423000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>16440000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>16214000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>15949000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>16844000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>13903100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>13722200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>15680800</v>
       </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2088,9 +2201,12 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3"/>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2124,45 +2240,51 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1047000</v>
+      </c>
+      <c r="E52" s="3">
         <v>909000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>540000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>568000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>619000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>446000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>383000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>271000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>978200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1051600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>582900</v>
       </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2196,45 +2318,51 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>24632000</v>
+      </c>
+      <c r="E54" s="3">
         <v>23391000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>22746000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>23246000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>22777000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>22360000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>20141000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>21224000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>19124900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>18411100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>21343000</v>
       </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2249,8 +2377,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2265,224 +2394,243 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>765000</v>
+      </c>
+      <c r="E57" s="3">
         <v>790000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>758000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>614000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>464000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>644000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>513000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>496000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>369800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>361500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>223000</v>
       </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3"/>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>415000</v>
+      </c>
+      <c r="E58" s="3">
         <v>248000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>264000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>236000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>248000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>227000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>91000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>78000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>93900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>56100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2173600</v>
       </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3"/>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>813000</v>
+      </c>
+      <c r="E59" s="3">
         <v>717000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>735000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>706000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>611000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>571000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>525000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>779000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>747000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>703400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>594000</v>
       </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2364000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2144000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2116000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1878000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1601000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1703000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1408000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1655000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1210700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1121000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1945800</v>
       </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>15511000</v>
+      </c>
+      <c r="E61" s="3">
         <v>14225000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>14177000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>14539000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>14224000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>13311000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>12121000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>12087000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8628600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8665700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>9070200</v>
       </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>112000</v>
+      </c>
+      <c r="E62" s="3">
         <v>350000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>248000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>987000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1180000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>892000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>903000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1304000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2500000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2414700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2690600</v>
       </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2516,9 +2664,12 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2552,9 +2703,12 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2588,45 +2742,51 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>19789000</v>
+      </c>
+      <c r="E66" s="3">
         <v>18661000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>18478000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>19393000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>19056000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>18101000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>16523000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>16663000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14125400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13777500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>16167800</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2641,8 +2801,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2676,9 +2837,12 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2712,9 +2876,12 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2740,7 +2907,7 @@
         <v>0</v>
       </c>
       <c r="K70" s="3">
-        <v>3297000</v>
+        <v>0</v>
       </c>
       <c r="L70" s="3">
         <v>3297000</v>
@@ -2748,9 +2915,12 @@
       <c r="M70" s="3">
         <v>3297000</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>3297000</v>
+      </c>
+      <c r="O70" s="3"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2784,45 +2954,51 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1860000</v>
+      </c>
+      <c r="E72" s="3">
         <v>1599000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1121000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>791000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>622000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>775000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>674000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>651000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>445700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>245800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>231000</v>
       </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2856,9 +3032,12 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2892,9 +3071,12 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2928,45 +3110,51 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3110000</v>
+      </c>
+      <c r="E76" s="3">
         <v>2866000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2499000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2237000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2167000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2490000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1611000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2227000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1702500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1336600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1878200</v>
       </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3000,86 +3188,95 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1021000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1190000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1008000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>838000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>486000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>643000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>612000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>648000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>345600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>103900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-398800</v>
       </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3094,44 +3291,48 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>206000</v>
+      </c>
+      <c r="E83" s="3">
         <v>154000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>151000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>160000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>146000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>141000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>110000</v>
       </c>
       <c r="J83" s="3">
         <v>110000</v>
       </c>
       <c r="K83" s="3">
+        <v>110000</v>
+      </c>
+      <c r="L83" s="3">
         <v>172100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>182000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>68800</v>
       </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3"/>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3165,9 +3366,12 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3201,9 +3405,12 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3237,9 +3444,12 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3273,9 +3483,12 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3309,45 +3522,51 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1503000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1323000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1490000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1726000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>921000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1476000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1165000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1391000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1269000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1204800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>259300</v>
       </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3362,44 +3581,48 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-201000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-120000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-100000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-106000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-117000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-62000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-86000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-37000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-33700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-115300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-38700</v>
       </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3433,9 +3656,12 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3469,45 +3695,51 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-660000</v>
+      </c>
+      <c r="E94" s="3">
         <v>11000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-64000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1103000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-79000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-30000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-44000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-858000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>26900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-61500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-7790800</v>
       </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3522,44 +3754,48 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1029000</v>
+      </c>
+      <c r="E96" s="3">
         <v>990000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>971000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>974000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>959000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>901000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>728000</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-538100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-362400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-105600</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3593,9 +3829,12 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3629,9 +3868,12 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3665,115 +3907,127 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-625000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1374000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1307000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1093000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-821000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-842000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1285000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-936000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-590900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2115200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>8565600</v>
       </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-23000</v>
+      </c>
+      <c r="E101" s="3">
         <v>1000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-28000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-3000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>6000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>16000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-20000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>24000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-73500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-17800</v>
       </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>195000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-39000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>91000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-473000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>27000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>620000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-184000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-379000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>702600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1045400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1016300</v>
       </c>
-      <c r="N102" s="3"/>
+      <c r="O102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/QSR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/QSR_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
   <si>
     <t>QSR</t>
   </si>
@@ -656,183 +656,195 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>9434000</v>
+      </c>
+      <c r="E8" s="3">
         <v>8406000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7022000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6505000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5739000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4968000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5603000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5357000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4576000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4145800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4052200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1198800</v>
       </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>6241000</v>
+      </c>
+      <c r="E9" s="3">
         <v>5382000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>4220000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3907000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3365000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2995000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3211000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2240000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2328000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1727300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1809500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>156400</v>
       </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3193000</v>
+      </c>
+      <c r="E10" s="3">
         <v>3024000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2802000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2598000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2374000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1973000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2392000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3117000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2248000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2418500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2242700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1042400</v>
       </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -848,8 +860,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -886,9 +899,12 @@
       <c r="N12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -925,87 +941,96 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>95000</v>
+      </c>
+      <c r="E14" s="3">
         <v>78000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>90000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>85000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>128000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>127000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>69000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>85000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>217000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>18000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>158000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>284400</v>
       </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>301000</v>
+      </c>
+      <c r="E15" s="3">
         <v>264000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>191000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>190000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>201000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>189000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>185000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>180000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>182000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>21700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>17000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>14000</v>
       </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1018,86 +1043,93 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6941000</v>
+      </c>
+      <c r="E17" s="3">
         <v>6082000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4885000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4482000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3815000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3378000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3576000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3410000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2681000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2479100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2900000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1173100</v>
       </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2493000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2324000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2137000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2023000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1924000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1590000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2027000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1947000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1895000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1666700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1152200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>25700</v>
       </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1113,203 +1145,219 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>198000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-140000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>12000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>40000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-72000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>139000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-26000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-55000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>65000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>4100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2800</v>
       </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2596000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2728000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2316000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2173000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2197000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1640000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2238000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2182000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2012000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1842900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1335800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>97300</v>
       </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>522000</v>
+      </c>
+      <c r="E22" s="3">
         <v>591000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>595000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>512000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>481000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>491000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>523000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>521000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>505000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>471000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>479900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>282500</v>
       </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1684000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1809000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1453000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1365000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1363000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>816000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1452000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1382000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1101000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1199800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>673900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-254000</v>
       </c>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>483000</v>
+      </c>
+      <c r="E24" s="3">
         <v>364000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-265000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-117000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>110000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>66000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>341000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>238000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-134000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>243900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>162200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>15300</v>
       </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1346,87 +1394,96 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1201000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1445000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1718000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1482000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1253000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>750000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1111000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1144000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1235000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>955900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>511700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-269300</v>
       </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>776000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1021000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1190000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1008000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>838000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>486000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>643000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>612000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>626000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>345600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>103900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-398800</v>
       </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1463,14 +1520,17 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>-126000</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
@@ -1493,8 +1553,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
@@ -1502,9 +1562,12 @@
       <c r="N29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1541,9 +1604,12 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1580,87 +1646,96 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-198000</v>
+      </c>
+      <c r="E32" s="3">
         <v>140000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-12000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-40000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>72000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-139000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>26000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>55000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-65000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-4100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2800</v>
       </c>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>776000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1021000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1190000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1008000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>838000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>486000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>643000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>612000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>648000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>345600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>103900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-398800</v>
       </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1697,92 +1772,101 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>776000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1021000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1190000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1008000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>838000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>486000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>643000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>612000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>648000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>345600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>103900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-398800</v>
       </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1798,8 +1882,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1815,56 +1900,60 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1163000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1334000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1139000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1178000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1087000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1560000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1533000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>913000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1097000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1460400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>757800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1803200</v>
       </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E42" s="3">
         <v>1000</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
@@ -1892,282 +1981,306 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>794000</v>
+      </c>
+      <c r="E43" s="3">
         <v>698000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>749000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>614000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>547000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>536000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>527000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>452000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>489000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>403500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>443500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>459500</v>
       </c>
-      <c r="O43" s="3"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>205000</v>
+      </c>
+      <c r="E44" s="3">
         <v>142000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>166000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>133000</v>
-      </c>
-      <c r="G44" s="3">
-        <v>96000</v>
       </c>
       <c r="H44" s="3">
         <v>96000</v>
       </c>
       <c r="I44" s="3">
+        <v>96000</v>
+      </c>
+      <c r="J44" s="3">
         <v>84000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>75000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>78000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>71800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>81300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>97800</v>
       </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>489000</v>
+      </c>
+      <c r="E45" s="3">
         <v>8000</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="F45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2000</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
         <v>7000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>161300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>86900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>300800</v>
       </c>
-      <c r="O45" s="3"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2830000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2282000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2173000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2048000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1816000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2264000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2196000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1500000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1750000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2097000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1369500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2640800</v>
       </c>
-      <c r="O46" s="3"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>169000</v>
+      </c>
+      <c r="E47" s="3">
         <v>307000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>353000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>447000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>194000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>205000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>273000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>259000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>155000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>91900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>117200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>140500</v>
       </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4264000</v>
+      </c>
+      <c r="E48" s="3">
         <v>4088000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3074000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3032000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3165000</v>
-      </c>
-      <c r="H48" s="3">
-        <v>3183000</v>
       </c>
       <c r="I48" s="3">
         <v>3183000</v>
       </c>
       <c r="J48" s="3">
+        <v>3183000</v>
+      </c>
+      <c r="K48" s="3">
         <v>1996000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2133000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2054700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2150600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5098700</v>
       </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>17496000</v>
+      </c>
+      <c r="E49" s="3">
         <v>16908000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>16882000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>16679000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>17423000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>16440000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>16214000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>15949000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>16844000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>13903100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>13722200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>15680800</v>
       </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2204,9 +2317,12 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2243,48 +2359,54 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>856000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1047000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>909000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>540000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>568000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>619000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>446000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>383000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>271000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>978200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1051600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>582900</v>
       </c>
-      <c r="O52" s="3"/>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2321,48 +2443,54 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3"/>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>25615000</v>
+      </c>
+      <c r="E54" s="3">
         <v>24632000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>23391000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>22746000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>23246000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>22777000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>22360000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>20141000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>21224000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>19124900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>18411100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>21343000</v>
       </c>
-      <c r="O54" s="3"/>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2378,8 +2506,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2395,242 +2524,261 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>866000</v>
+      </c>
+      <c r="E57" s="3">
         <v>765000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>790000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>758000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>614000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>464000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>644000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>513000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>496000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>369800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>361500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>223000</v>
       </c>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>268000</v>
+      </c>
+      <c r="E58" s="3">
         <v>415000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>248000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>264000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>236000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>248000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>227000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>91000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>78000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>93900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>56100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2173600</v>
       </c>
-      <c r="O58" s="3"/>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1259000</v>
+      </c>
+      <c r="E59" s="3">
         <v>813000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>717000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>735000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>706000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>611000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>571000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>525000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>779000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>747000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>703400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>594000</v>
       </c>
-      <c r="O59" s="3"/>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2891000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2364000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2144000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2116000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1878000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1601000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1703000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1408000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1655000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1210700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1121000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1945800</v>
       </c>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>15411000</v>
+      </c>
+      <c r="E61" s="3">
         <v>15511000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>14225000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>14177000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>14539000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>14224000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>13311000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>12121000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>12087000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8628600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8665700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>9070200</v>
       </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>449000</v>
+      </c>
+      <c r="E62" s="3">
         <v>112000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>350000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>248000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>987000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1180000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>892000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>903000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1304000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2500000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2414700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2690600</v>
       </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2667,9 +2815,12 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2706,9 +2857,12 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-      <c r="O64" s="3"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2745,48 +2899,54 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>20456000</v>
+      </c>
+      <c r="E66" s="3">
         <v>19789000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>18661000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>18478000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>19393000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>19056000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>18101000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>16523000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>16663000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14125400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13777500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>16167800</v>
       </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2802,8 +2962,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2840,9 +3001,12 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2879,9 +3043,12 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2910,7 +3077,7 @@
         <v>0</v>
       </c>
       <c r="L70" s="3">
-        <v>3297000</v>
+        <v>0</v>
       </c>
       <c r="M70" s="3">
         <v>3297000</v>
@@ -2918,9 +3085,12 @@
       <c r="N70" s="3">
         <v>3297000</v>
       </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>3297000</v>
+      </c>
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2957,48 +3127,54 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1795000</v>
+      </c>
+      <c r="E72" s="3">
         <v>1860000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1599000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1121000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>791000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>622000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>775000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>674000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>651000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>445700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>245800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>231000</v>
       </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3035,9 +3211,12 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3074,9 +3253,12 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3113,48 +3295,54 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3634000</v>
+      </c>
+      <c r="E76" s="3">
         <v>3110000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2866000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2499000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2237000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2167000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2490000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1611000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2227000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1702500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1336600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1878200</v>
       </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3191,92 +3379,101 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>776000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1021000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1190000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1008000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>838000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>486000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>643000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>612000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>648000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>345600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>103900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-398800</v>
       </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3292,47 +3489,51 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>232000</v>
+      </c>
+      <c r="E83" s="3">
         <v>206000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>154000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>151000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>160000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>146000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>141000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>110000</v>
       </c>
       <c r="K83" s="3">
         <v>110000</v>
       </c>
       <c r="L83" s="3">
+        <v>110000</v>
+      </c>
+      <c r="M83" s="3">
         <v>172100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>182000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>68800</v>
       </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3369,9 +3570,12 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3408,9 +3612,12 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3447,9 +3654,12 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3486,9 +3696,12 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3525,48 +3738,54 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-      <c r="O88" s="3"/>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1567000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1503000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1323000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1490000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1726000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>921000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1476000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1165000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1391000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1269000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1204800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>259300</v>
       </c>
-      <c r="O89" s="3"/>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3582,47 +3801,51 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-265000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-201000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-120000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-100000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-106000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-117000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-62000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-86000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-37000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-33700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-115300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-38700</v>
       </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3659,9 +3882,12 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-      <c r="O92" s="3"/>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3698,48 +3924,54 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-318000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-660000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>11000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-64000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1103000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-79000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-30000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-44000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-858000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>26900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-61500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-7790800</v>
       </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3755,47 +3987,51 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1108000</v>
+      </c>
+      <c r="E96" s="3">
         <v>1029000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>990000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>971000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>974000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>959000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>901000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>728000</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-538100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-362400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-105600</v>
       </c>
-      <c r="O96" s="3"/>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3832,9 +4068,12 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3871,9 +4110,12 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3910,124 +4152,136 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1436000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-625000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1374000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1307000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1093000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-821000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-842000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1285000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-936000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-590900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2115200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>8565600</v>
       </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-23000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-28000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-3000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>6000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>16000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-20000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>24000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-73500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-17800</v>
       </c>
-      <c r="O101" s="3"/>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-171000</v>
+      </c>
+      <c r="E102" s="3">
         <v>195000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-39000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>91000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-473000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>27000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>620000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-184000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-379000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>702600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1045400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1016300</v>
       </c>
-      <c r="O102" s="3"/>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
